--- a/InputData/elec/MCF/Maximum Capacity Factor.xlsx
+++ b/InputData/elec/MCF/Maximum Capacity Factor.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\elec\MCF\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mary Francis Swint\Vensim\eps-indonesia\InputData\elec\MCF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB4EA080-2835-46E2-ACAA-C8B525FFB4D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{819F9430-F7F5-413E-8A60-AE71740DB398}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="31935" yWindow="3675" windowWidth="19200" windowHeight="11205" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="12" r:id="rId1"/>
@@ -627,7 +627,7 @@
     <numFmt numFmtId="164" formatCode="0.0000"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="29" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1850,23 +1850,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H25"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.28515625" customWidth="1"/>
-    <col min="2" max="2" width="50.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="49.5703125" customWidth="1"/>
-    <col min="8" max="8" width="53.7109375" customWidth="1"/>
+    <col min="1" max="1" width="9.26953125" customWidth="1"/>
+    <col min="2" max="2" width="50.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="49.54296875" customWidth="1"/>
+    <col min="8" max="8" width="53.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="G2" s="2"/>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
@@ -1876,7 +1876,7 @@
       <c r="E3" s="1"/>
       <c r="H3" s="1"/>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
       <c r="B4" t="s">
         <v>22</v>
@@ -1884,7 +1884,7 @@
       <c r="E4" s="1"/>
       <c r="H4" s="1"/>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="1"/>
       <c r="B5" s="2">
         <v>2019</v>
@@ -1892,7 +1892,7 @@
       <c r="E5" s="1"/>
       <c r="H5" s="1"/>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
       <c r="B6" t="s">
         <v>23</v>
@@ -1900,99 +1900,99 @@
       <c r="E6" s="1"/>
       <c r="H6" s="1"/>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B7" s="4" t="s">
         <v>24</v>
       </c>
       <c r="H7" s="2"/>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="H8" s="2"/>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B9" s="101" t="s">
         <v>129</v>
       </c>
       <c r="H9" s="2"/>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
         <v>130</v>
       </c>
       <c r="H10" s="2"/>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
         <v>131</v>
       </c>
       <c r="H11" s="2"/>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B12" s="2">
         <v>2024</v>
       </c>
       <c r="H12" s="2"/>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B13" t="s">
         <v>132</v>
       </c>
       <c r="H13" s="2"/>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B14" t="s">
         <v>133</v>
       </c>
       <c r="H14" s="2"/>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="H15" s="2"/>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>7</v>
       </c>
       <c r="H16" s="2"/>
     </row>
-    <row r="17" spans="1:8">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>20</v>
       </c>
       <c r="H17" s="2"/>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>34</v>
       </c>
       <c r="H18" s="4"/>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>21</v>
       </c>
       <c r="H19" s="2"/>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="24" spans="1:8">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="25" spans="1:8">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>128</v>
       </c>
@@ -2014,14 +2014,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0150863A-DAB8-46CE-A81F-C1B3C520912B}">
   <dimension ref="A1:N158"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="65.28515625" style="58" customWidth="1"/>
+    <col min="1" max="1" width="65.26953125" style="58" customWidth="1"/>
     <col min="2" max="2" width="2" style="58" customWidth="1"/>
-    <col min="3" max="8" width="8.42578125" style="9" customWidth="1"/>
+    <col min="3" max="8" width="8.453125" style="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" s="8"/>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -2030,7 +2030,7 @@
       <c r="F1" s="8"/>
       <c r="G1"/>
     </row>
-    <row r="2" spans="1:14" ht="26.25">
+    <row r="2" spans="1:14" ht="25" x14ac:dyDescent="0.5">
       <c r="A2" s="102" t="s">
         <v>35</v>
       </c>
@@ -2041,7 +2041,7 @@
       <c r="F2" s="102"/>
       <c r="G2" s="102"/>
     </row>
-    <row r="3" spans="1:14" ht="18">
+    <row r="3" spans="1:14" ht="18" x14ac:dyDescent="0.4">
       <c r="A3" s="8"/>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
@@ -2054,7 +2054,7 @@
       <c r="M3" s="103"/>
       <c r="N3" s="103"/>
     </row>
-    <row r="4" spans="1:14" ht="18">
+    <row r="4" spans="1:14" ht="18" x14ac:dyDescent="0.4">
       <c r="A4" s="104" t="s">
         <v>36</v>
       </c>
@@ -2065,7 +2065,7 @@
       <c r="F4" s="104"/>
       <c r="G4" s="104"/>
     </row>
-    <row r="5" spans="1:14" ht="18">
+    <row r="5" spans="1:14" ht="18" x14ac:dyDescent="0.4">
       <c r="A5" s="8"/>
       <c r="B5" s="103"/>
       <c r="C5" s="103"/>
@@ -2074,7 +2074,7 @@
       <c r="F5" s="8"/>
       <c r="G5"/>
     </row>
-    <row r="6" spans="1:14" ht="15.75">
+    <row r="6" spans="1:14" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A6" s="10"/>
       <c r="B6" s="10"/>
       <c r="C6" s="10" t="s">
@@ -2085,7 +2085,7 @@
       <c r="F6" s="10"/>
       <c r="G6" s="10"/>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7" s="105"/>
       <c r="B7" s="105"/>
       <c r="C7" s="105"/>
@@ -2094,7 +2094,7 @@
       <c r="F7" s="105"/>
       <c r="G7" s="105"/>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8" s="12"/>
       <c r="B8" s="12"/>
       <c r="C8" s="12"/>
@@ -2103,7 +2103,7 @@
       <c r="F8" s="12"/>
       <c r="G8" s="12"/>
     </row>
-    <row r="9" spans="1:14" ht="15.75" thickBot="1">
+    <row r="9" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" s="13" t="s">
         <v>38</v>
       </c>
@@ -2112,7 +2112,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="18.75" thickBot="1">
+    <row r="10" spans="1:14" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A10" s="15" t="s">
         <v>40</v>
       </c>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="J10" s="19"/>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11" s="20" t="s">
         <v>41</v>
       </c>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="J11" s="26"/>
     </row>
-    <row r="12" spans="1:14">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12" s="27" t="s">
         <v>42</v>
       </c>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="J12" s="31"/>
     </row>
-    <row r="13" spans="1:14">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13" s="20" t="s">
         <v>43</v>
       </c>
@@ -2224,7 +2224,7 @@
       </c>
       <c r="J13" s="34"/>
     </row>
-    <row r="14" spans="1:14">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" s="27" t="s">
         <v>44</v>
       </c>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="J14" s="37"/>
     </row>
-    <row r="15" spans="1:14" ht="15.75" thickBot="1">
+    <row r="15" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A15" s="38" t="s">
         <v>45</v>
       </c>
@@ -2280,7 +2280,7 @@
       </c>
       <c r="J15" s="37"/>
     </row>
-    <row r="16" spans="1:14" ht="15.75" thickBot="1">
+    <row r="16" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A16" s="21"/>
       <c r="B16" s="21"/>
       <c r="C16" s="43"/>
@@ -2290,7 +2290,7 @@
       <c r="G16" s="43"/>
       <c r="H16" s="44"/>
     </row>
-    <row r="17" spans="1:10" ht="18.75" thickBot="1">
+    <row r="17" spans="1:10" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A17" s="15" t="s">
         <v>46</v>
       </c>
@@ -2318,7 +2318,7 @@
       </c>
       <c r="J17" s="19"/>
     </row>
-    <row r="18" spans="1:10" ht="15.75" thickBot="1">
+    <row r="18" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A18" s="45" t="s">
         <v>47</v>
       </c>
@@ -2346,7 +2346,7 @@
       </c>
       <c r="J18" s="49"/>
     </row>
-    <row r="19" spans="1:10" ht="15.75" thickBot="1">
+    <row r="19" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="21"/>
       <c r="B19" s="21"/>
       <c r="C19" s="50"/>
@@ -2356,7 +2356,7 @@
       <c r="G19" s="50"/>
       <c r="H19" s="51"/>
     </row>
-    <row r="20" spans="1:10" ht="18.75" thickBot="1">
+    <row r="20" spans="1:10" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A20" s="15" t="s">
         <v>48</v>
       </c>
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J20" s="19"/>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21" s="20" t="s">
         <v>49</v>
       </c>
@@ -2412,7 +2412,7 @@
       </c>
       <c r="J21" s="54"/>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A22" s="27" t="s">
         <v>50</v>
       </c>
@@ -2426,7 +2426,7 @@
       <c r="I22" s="56"/>
       <c r="J22" s="54"/>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A23" s="57" t="s">
         <v>51</v>
       </c>
@@ -2453,7 +2453,7 @@
       </c>
       <c r="J23" s="54"/>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24" s="59" t="s">
         <v>52</v>
       </c>
@@ -2481,7 +2481,7 @@
       </c>
       <c r="J24" s="54"/>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A25" s="20" t="s">
         <v>53</v>
       </c>
@@ -2495,7 +2495,7 @@
       <c r="I25" s="53"/>
       <c r="J25" s="54"/>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26" s="59" t="s">
         <v>54</v>
       </c>
@@ -2523,7 +2523,7 @@
       </c>
       <c r="J26" s="54"/>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A27" s="57" t="s">
         <v>55</v>
       </c>
@@ -2542,7 +2542,7 @@
       <c r="I27" s="53"/>
       <c r="J27" s="54"/>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A28" s="59" t="s">
         <v>56</v>
       </c>
@@ -2570,7 +2570,7 @@
       </c>
       <c r="J28" s="54"/>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A29" s="57" t="s">
         <v>57</v>
       </c>
@@ -2591,7 +2591,7 @@
       <c r="I29" s="53"/>
       <c r="J29" s="54"/>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A30" s="59" t="s">
         <v>58</v>
       </c>
@@ -2619,7 +2619,7 @@
       </c>
       <c r="J30" s="54"/>
     </row>
-    <row r="31" spans="1:10" ht="15.75" thickBot="1">
+    <row r="31" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A31" s="61" t="s">
         <v>59</v>
       </c>
@@ -2647,7 +2647,7 @@
       </c>
       <c r="J31" s="54"/>
     </row>
-    <row r="32" spans="1:10" ht="15.75" thickBot="1">
+    <row r="32" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A32" s="21"/>
       <c r="B32" s="21"/>
       <c r="C32" s="65"/>
@@ -2657,7 +2657,7 @@
       <c r="G32" s="65"/>
       <c r="H32" s="65"/>
     </row>
-    <row r="33" spans="1:10" ht="18.75" thickBot="1">
+    <row r="33" spans="1:10" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A33" s="15" t="s">
         <v>60</v>
       </c>
@@ -2685,7 +2685,7 @@
       </c>
       <c r="J33" s="19"/>
     </row>
-    <row r="34" spans="1:10">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A34" s="20" t="s">
         <v>61</v>
       </c>
@@ -2713,7 +2713,7 @@
       </c>
       <c r="J34" s="68"/>
     </row>
-    <row r="35" spans="1:10">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A35" s="27" t="s">
         <v>62</v>
       </c>
@@ -2741,7 +2741,7 @@
       </c>
       <c r="J35" s="68"/>
     </row>
-    <row r="36" spans="1:10">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A36" s="57" t="s">
         <v>63</v>
       </c>
@@ -2769,7 +2769,7 @@
       </c>
       <c r="J36" s="68"/>
     </row>
-    <row r="37" spans="1:10">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A37" s="59" t="s">
         <v>64</v>
       </c>
@@ -2797,7 +2797,7 @@
       </c>
       <c r="J37" s="68"/>
     </row>
-    <row r="38" spans="1:10" s="73" customFormat="1" ht="14.25">
+    <row r="38" spans="1:10" s="73" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A38" s="57" t="s">
         <v>65</v>
       </c>
@@ -2825,7 +2825,7 @@
       </c>
       <c r="J38" s="68"/>
     </row>
-    <row r="39" spans="1:10" s="73" customFormat="1" ht="14.25">
+    <row r="39" spans="1:10" s="73" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A39" s="59" t="s">
         <v>66</v>
       </c>
@@ -2853,7 +2853,7 @@
       </c>
       <c r="J39" s="68"/>
     </row>
-    <row r="40" spans="1:10" s="73" customFormat="1" ht="14.25">
+    <row r="40" spans="1:10" s="73" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A40" s="57" t="s">
         <v>67</v>
       </c>
@@ -2881,7 +2881,7 @@
       </c>
       <c r="J40" s="68"/>
     </row>
-    <row r="41" spans="1:10" s="73" customFormat="1" ht="14.25">
+    <row r="41" spans="1:10" s="73" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A41" s="59" t="s">
         <v>68</v>
       </c>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="J41" s="68"/>
     </row>
-    <row r="42" spans="1:10">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A42" s="20" t="s">
         <v>69</v>
       </c>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="J42" s="68"/>
     </row>
-    <row r="43" spans="1:10" s="73" customFormat="1" ht="14.25">
+    <row r="43" spans="1:10" s="73" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A43" s="59" t="s">
         <v>70</v>
       </c>
@@ -2964,7 +2964,7 @@
       </c>
       <c r="J43" s="68"/>
     </row>
-    <row r="44" spans="1:10" s="73" customFormat="1" ht="14.25">
+    <row r="44" spans="1:10" s="73" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A44" s="57" t="s">
         <v>71</v>
       </c>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="J44" s="68"/>
     </row>
-    <row r="45" spans="1:10" s="73" customFormat="1" ht="14.25">
+    <row r="45" spans="1:10" s="73" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A45" s="59" t="s">
         <v>72</v>
       </c>
@@ -3020,7 +3020,7 @@
       </c>
       <c r="J45" s="68"/>
     </row>
-    <row r="46" spans="1:10">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A46" s="20" t="s">
         <v>73</v>
       </c>
@@ -3047,7 +3047,7 @@
       </c>
       <c r="J46" s="68"/>
     </row>
-    <row r="47" spans="1:10">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A47" s="27" t="s">
         <v>74</v>
       </c>
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J47" s="68"/>
     </row>
-    <row r="48" spans="1:10">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A48" s="20" t="s">
         <v>75</v>
       </c>
@@ -3102,7 +3102,7 @@
       </c>
       <c r="J48" s="68"/>
     </row>
-    <row r="49" spans="1:10" s="73" customFormat="1" ht="14.25">
+    <row r="49" spans="1:10" s="73" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A49" s="59" t="s">
         <v>76</v>
       </c>
@@ -3130,7 +3130,7 @@
       </c>
       <c r="J49" s="68"/>
     </row>
-    <row r="50" spans="1:10" s="73" customFormat="1" ht="14.25">
+    <row r="50" spans="1:10" s="73" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A50" s="57" t="s">
         <v>77</v>
       </c>
@@ -3158,7 +3158,7 @@
       </c>
       <c r="J50" s="68"/>
     </row>
-    <row r="51" spans="1:10">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A51" s="59" t="s">
         <v>78</v>
       </c>
@@ -3186,7 +3186,7 @@
       </c>
       <c r="J51" s="68"/>
     </row>
-    <row r="52" spans="1:10">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A52" s="20" t="s">
         <v>79</v>
       </c>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="J52" s="68"/>
     </row>
-    <row r="53" spans="1:10">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A53" s="27" t="s">
         <v>80</v>
       </c>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="J53" s="68"/>
     </row>
-    <row r="54" spans="1:10" ht="15.75" thickBot="1">
+    <row r="54" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A54" s="76" t="s">
         <v>81</v>
       </c>
@@ -3269,7 +3269,7 @@
       </c>
       <c r="J54" s="68"/>
     </row>
-    <row r="55" spans="1:10" ht="16.5" thickTop="1" thickBot="1">
+    <row r="55" spans="1:10" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A55" s="21"/>
       <c r="B55" s="21"/>
       <c r="C55" s="66"/>
@@ -3279,7 +3279,7 @@
       <c r="G55" s="66"/>
       <c r="H55" s="66"/>
     </row>
-    <row r="56" spans="1:10" ht="18.75" thickBot="1">
+    <row r="56" spans="1:10" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A56" s="15" t="s">
         <v>82</v>
       </c>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="J56" s="19"/>
     </row>
-    <row r="57" spans="1:10">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A57" s="20" t="s">
         <v>61</v>
       </c>
@@ -3335,7 +3335,7 @@
       </c>
       <c r="J57" s="37"/>
     </row>
-    <row r="58" spans="1:10">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A58" s="27" t="s">
         <v>62</v>
       </c>
@@ -3363,7 +3363,7 @@
       </c>
       <c r="J58" s="81"/>
     </row>
-    <row r="59" spans="1:10">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A59" s="57" t="s">
         <v>63</v>
       </c>
@@ -3391,7 +3391,7 @@
       </c>
       <c r="J59" s="81"/>
     </row>
-    <row r="60" spans="1:10">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A60" s="59" t="s">
         <v>64</v>
       </c>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="J60" s="81"/>
     </row>
-    <row r="61" spans="1:10" s="73" customFormat="1" ht="14.25">
+    <row r="61" spans="1:10" s="73" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A61" s="57" t="s">
         <v>65</v>
       </c>
@@ -3447,7 +3447,7 @@
       </c>
       <c r="J61" s="81"/>
     </row>
-    <row r="62" spans="1:10" s="73" customFormat="1" ht="14.25">
+    <row r="62" spans="1:10" s="73" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A62" s="59" t="s">
         <v>66</v>
       </c>
@@ -3475,7 +3475,7 @@
       </c>
       <c r="J62" s="81"/>
     </row>
-    <row r="63" spans="1:10" s="73" customFormat="1" ht="14.25">
+    <row r="63" spans="1:10" s="73" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A63" s="57" t="s">
         <v>67</v>
       </c>
@@ -3503,7 +3503,7 @@
       </c>
       <c r="J63" s="81"/>
     </row>
-    <row r="64" spans="1:10">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A64" s="27" t="s">
         <v>69</v>
       </c>
@@ -3531,7 +3531,7 @@
       </c>
       <c r="J64" s="81"/>
     </row>
-    <row r="65" spans="1:10" s="73" customFormat="1" ht="14.25">
+    <row r="65" spans="1:10" s="73" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A65" s="57" t="s">
         <v>70</v>
       </c>
@@ -3559,7 +3559,7 @@
       </c>
       <c r="J65" s="81"/>
     </row>
-    <row r="66" spans="1:10" s="73" customFormat="1" ht="14.25">
+    <row r="66" spans="1:10" s="73" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A66" s="82" t="s">
         <v>71</v>
       </c>
@@ -3587,7 +3587,7 @@
       </c>
       <c r="J66" s="81"/>
     </row>
-    <row r="67" spans="1:10" s="73" customFormat="1" ht="14.25">
+    <row r="67" spans="1:10" s="73" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A67" s="57" t="s">
         <v>72</v>
       </c>
@@ -3615,7 +3615,7 @@
       </c>
       <c r="J67" s="81"/>
     </row>
-    <row r="68" spans="1:10">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A68" s="27" t="s">
         <v>73</v>
       </c>
@@ -3643,7 +3643,7 @@
       </c>
       <c r="J68" s="81"/>
     </row>
-    <row r="69" spans="1:10">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A69" s="20" t="s">
         <v>74</v>
       </c>
@@ -3671,7 +3671,7 @@
       </c>
       <c r="J69" s="81"/>
     </row>
-    <row r="70" spans="1:10">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A70" s="27" t="s">
         <v>75</v>
       </c>
@@ -3699,7 +3699,7 @@
       </c>
       <c r="J70" s="81"/>
     </row>
-    <row r="71" spans="1:10" s="73" customFormat="1" ht="14.25">
+    <row r="71" spans="1:10" s="73" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A71" s="57" t="s">
         <v>76</v>
       </c>
@@ -3727,7 +3727,7 @@
       </c>
       <c r="J71" s="81"/>
     </row>
-    <row r="72" spans="1:10" s="73" customFormat="1" ht="14.25">
+    <row r="72" spans="1:10" s="73" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A72" s="83" t="s">
         <v>77</v>
       </c>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="J72" s="81"/>
     </row>
-    <row r="73" spans="1:10">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A73" s="57" t="s">
         <v>78</v>
       </c>
@@ -3783,7 +3783,7 @@
       </c>
       <c r="J73" s="81"/>
     </row>
-    <row r="74" spans="1:10">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A74" s="27" t="s">
         <v>80</v>
       </c>
@@ -3811,7 +3811,7 @@
       </c>
       <c r="J74" s="81"/>
     </row>
-    <row r="75" spans="1:10" ht="15.75" thickBot="1">
+    <row r="75" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A75" s="84" t="s">
         <v>81</v>
       </c>
@@ -3839,7 +3839,7 @@
       </c>
       <c r="J75" s="81"/>
     </row>
-    <row r="76" spans="1:10" ht="15.75" thickBot="1">
+    <row r="76" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A76" s="38"/>
       <c r="B76" s="39"/>
       <c r="C76" s="88"/>
@@ -3851,7 +3851,7 @@
       <c r="I76" s="88"/>
       <c r="J76" s="81"/>
     </row>
-    <row r="77" spans="1:10" ht="18.75" thickBot="1">
+    <row r="77" spans="1:10" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A77" s="15" t="s">
         <v>83</v>
       </c>
@@ -3879,7 +3879,7 @@
       </c>
       <c r="J77" s="19"/>
     </row>
-    <row r="78" spans="1:10">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A78" s="20" t="s">
         <v>61</v>
       </c>
@@ -3907,7 +3907,7 @@
       </c>
       <c r="J78" s="37"/>
     </row>
-    <row r="79" spans="1:10">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A79" s="27" t="s">
         <v>62</v>
       </c>
@@ -3935,7 +3935,7 @@
       </c>
       <c r="J79" s="81"/>
     </row>
-    <row r="80" spans="1:10">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A80" s="57" t="s">
         <v>63</v>
       </c>
@@ -3963,7 +3963,7 @@
       </c>
       <c r="J80" s="81"/>
     </row>
-    <row r="81" spans="1:10">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A81" s="59" t="s">
         <v>64</v>
       </c>
@@ -3991,7 +3991,7 @@
       </c>
       <c r="J81" s="81"/>
     </row>
-    <row r="82" spans="1:10" s="73" customFormat="1" ht="14.25">
+    <row r="82" spans="1:10" s="73" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A82" s="57" t="s">
         <v>65</v>
       </c>
@@ -4019,7 +4019,7 @@
       </c>
       <c r="J82" s="81"/>
     </row>
-    <row r="83" spans="1:10" s="73" customFormat="1" ht="14.25">
+    <row r="83" spans="1:10" s="73" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A83" s="59" t="s">
         <v>66</v>
       </c>
@@ -4047,7 +4047,7 @@
       </c>
       <c r="J83" s="81"/>
     </row>
-    <row r="84" spans="1:10" s="73" customFormat="1" ht="14.25">
+    <row r="84" spans="1:10" s="73" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A84" s="57" t="s">
         <v>67</v>
       </c>
@@ -4075,7 +4075,7 @@
       </c>
       <c r="J84" s="81"/>
     </row>
-    <row r="85" spans="1:10">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A85" s="27" t="s">
         <v>69</v>
       </c>
@@ -4103,7 +4103,7 @@
       </c>
       <c r="J85" s="81"/>
     </row>
-    <row r="86" spans="1:10" s="73" customFormat="1" ht="14.25">
+    <row r="86" spans="1:10" s="73" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A86" s="57" t="s">
         <v>70</v>
       </c>
@@ -4131,7 +4131,7 @@
       </c>
       <c r="J86" s="81"/>
     </row>
-    <row r="87" spans="1:10" s="73" customFormat="1" ht="14.25">
+    <row r="87" spans="1:10" s="73" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A87" s="82" t="s">
         <v>71</v>
       </c>
@@ -4159,7 +4159,7 @@
       </c>
       <c r="J87" s="81"/>
     </row>
-    <row r="88" spans="1:10" s="73" customFormat="1" ht="14.25">
+    <row r="88" spans="1:10" s="73" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A88" s="57" t="s">
         <v>72</v>
       </c>
@@ -4187,7 +4187,7 @@
       </c>
       <c r="J88" s="81"/>
     </row>
-    <row r="89" spans="1:10">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A89" s="27" t="s">
         <v>73</v>
       </c>
@@ -4215,7 +4215,7 @@
       </c>
       <c r="J89" s="81"/>
     </row>
-    <row r="90" spans="1:10">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A90" s="20" t="s">
         <v>74</v>
       </c>
@@ -4243,7 +4243,7 @@
       </c>
       <c r="J90" s="81"/>
     </row>
-    <row r="91" spans="1:10">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A91" s="27" t="s">
         <v>75</v>
       </c>
@@ -4271,7 +4271,7 @@
       </c>
       <c r="J91" s="81"/>
     </row>
-    <row r="92" spans="1:10" s="73" customFormat="1" ht="14.25">
+    <row r="92" spans="1:10" s="73" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A92" s="57" t="s">
         <v>76</v>
       </c>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="J92" s="81"/>
     </row>
-    <row r="93" spans="1:10" s="73" customFormat="1" ht="14.25">
+    <row r="93" spans="1:10" s="73" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A93" s="83" t="s">
         <v>77</v>
       </c>
@@ -4327,7 +4327,7 @@
       </c>
       <c r="J93" s="81"/>
     </row>
-    <row r="94" spans="1:10">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A94" s="57" t="s">
         <v>78</v>
       </c>
@@ -4355,7 +4355,7 @@
       </c>
       <c r="J94" s="81"/>
     </row>
-    <row r="95" spans="1:10">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A95" s="27" t="s">
         <v>80</v>
       </c>
@@ -4383,7 +4383,7 @@
       </c>
       <c r="J95" s="81"/>
     </row>
-    <row r="96" spans="1:10" ht="15.75" thickBot="1">
+    <row r="96" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A96" s="84" t="s">
         <v>81</v>
       </c>
@@ -4411,7 +4411,7 @@
       </c>
       <c r="J96" s="81"/>
     </row>
-    <row r="97" spans="1:10" ht="15.75" thickBot="1">
+    <row r="97" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A97" s="21"/>
       <c r="B97" s="21"/>
       <c r="C97" s="66"/>
@@ -4421,7 +4421,7 @@
       <c r="G97" s="66"/>
       <c r="H97" s="66"/>
     </row>
-    <row r="98" spans="1:10" ht="18.75" thickBot="1">
+    <row r="98" spans="1:10" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A98" s="15" t="s">
         <v>84</v>
       </c>
@@ -4449,7 +4449,7 @@
       </c>
       <c r="J98" s="19"/>
     </row>
-    <row r="99" spans="1:10">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A99" s="57" t="s">
         <v>85</v>
       </c>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="J99" s="81"/>
     </row>
-    <row r="100" spans="1:10">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A100" s="59" t="s">
         <v>86</v>
       </c>
@@ -4504,7 +4504,7 @@
       </c>
       <c r="J100" s="81"/>
     </row>
-    <row r="101" spans="1:10">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A101" s="57" t="s">
         <v>87</v>
       </c>
@@ -4531,7 +4531,7 @@
       </c>
       <c r="J101" s="81"/>
     </row>
-    <row r="102" spans="1:10">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A102" s="59" t="s">
         <v>88</v>
       </c>
@@ -4559,7 +4559,7 @@
       </c>
       <c r="J102" s="81"/>
     </row>
-    <row r="103" spans="1:10">
+    <row r="103" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A103" s="57" t="s">
         <v>89</v>
       </c>
@@ -4586,7 +4586,7 @@
       </c>
       <c r="J103" s="81"/>
     </row>
-    <row r="104" spans="1:10">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A104" s="59" t="s">
         <v>90</v>
       </c>
@@ -4614,7 +4614,7 @@
       </c>
       <c r="J104" s="81"/>
     </row>
-    <row r="105" spans="1:10">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A105" s="57" t="s">
         <v>91</v>
       </c>
@@ -4641,7 +4641,7 @@
       </c>
       <c r="J105" s="81"/>
     </row>
-    <row r="106" spans="1:10">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A106" s="60" t="s">
         <v>92</v>
       </c>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="J106" s="81"/>
     </row>
-    <row r="107" spans="1:10">
+    <row r="107" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A107" s="58" t="s">
         <v>93</v>
       </c>
@@ -4696,7 +4696,7 @@
       </c>
       <c r="J107" s="68"/>
     </row>
-    <row r="108" spans="1:10">
+    <row r="108" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A108" s="60" t="s">
         <v>94</v>
       </c>
@@ -4723,7 +4723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:10">
+    <row r="109" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A109" s="58" t="s">
         <v>95</v>
       </c>
@@ -4750,7 +4750,7 @@
       </c>
       <c r="J109" s="19"/>
     </row>
-    <row r="110" spans="1:10">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A110" s="60" t="s">
         <v>96</v>
       </c>
@@ -4778,7 +4778,7 @@
       </c>
       <c r="J110" s="68"/>
     </row>
-    <row r="111" spans="1:10" s="73" customFormat="1" ht="14.25">
+    <row r="111" spans="1:10" s="73" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A111" s="58" t="s">
         <v>97</v>
       </c>
@@ -4806,7 +4806,7 @@
       </c>
       <c r="J111" s="68"/>
     </row>
-    <row r="112" spans="1:10" s="73" customFormat="1" ht="14.25">
+    <row r="112" spans="1:10" s="73" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A112" s="60" t="s">
         <v>98</v>
       </c>
@@ -4834,7 +4834,7 @@
       </c>
       <c r="J112" s="68"/>
     </row>
-    <row r="113" spans="1:10" s="73" customFormat="1" ht="15.75" thickBot="1">
+    <row r="113" spans="1:10" s="73" customFormat="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A113" s="84" t="s">
         <v>81</v>
       </c>
@@ -4862,7 +4862,7 @@
       </c>
       <c r="J113" s="68"/>
     </row>
-    <row r="114" spans="1:10" s="73" customFormat="1" ht="15.75" thickBot="1">
+    <row r="114" spans="1:10" s="73" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A114" s="58"/>
       <c r="B114" s="58"/>
       <c r="C114" s="66"/>
@@ -4874,7 +4874,7 @@
       <c r="I114"/>
       <c r="J114" s="68"/>
     </row>
-    <row r="115" spans="1:10" s="73" customFormat="1" ht="18.75" thickBot="1">
+    <row r="115" spans="1:10" s="73" customFormat="1" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A115" s="15" t="s">
         <v>99</v>
       </c>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="J115" s="68"/>
     </row>
-    <row r="116" spans="1:10" s="73" customFormat="1">
+    <row r="116" spans="1:10" s="73" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A116" s="20" t="s">
         <v>61</v>
       </c>
@@ -4930,7 +4930,7 @@
       </c>
       <c r="J116" s="68"/>
     </row>
-    <row r="117" spans="1:10">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A117" s="27" t="s">
         <v>62</v>
       </c>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="J117" s="92"/>
     </row>
-    <row r="118" spans="1:10" s="73" customFormat="1">
+    <row r="118" spans="1:10" s="73" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A118" s="57" t="s">
         <v>63</v>
       </c>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="J118" s="68"/>
     </row>
-    <row r="119" spans="1:10" s="73" customFormat="1">
+    <row r="119" spans="1:10" s="73" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A119" s="59" t="s">
         <v>100</v>
       </c>
@@ -5014,7 +5014,7 @@
       </c>
       <c r="J119" s="68"/>
     </row>
-    <row r="120" spans="1:10" s="73" customFormat="1" ht="14.25">
+    <row r="120" spans="1:10" s="73" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A120" s="57" t="s">
         <v>64</v>
       </c>
@@ -5042,7 +5042,7 @@
       </c>
       <c r="J120" s="68"/>
     </row>
-    <row r="121" spans="1:10">
+    <row r="121" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A121" s="59" t="s">
         <v>65</v>
       </c>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="J121" s="68"/>
     </row>
-    <row r="122" spans="1:10">
+    <row r="122" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A122" s="57" t="s">
         <v>66</v>
       </c>
@@ -5097,7 +5097,7 @@
       </c>
       <c r="J122" s="68"/>
     </row>
-    <row r="123" spans="1:10">
+    <row r="123" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A123" s="59" t="s">
         <v>67</v>
       </c>
@@ -5125,7 +5125,7 @@
       </c>
       <c r="J123" s="68"/>
     </row>
-    <row r="124" spans="1:10">
+    <row r="124" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A124" s="57" t="s">
         <v>68</v>
       </c>
@@ -5152,7 +5152,7 @@
       </c>
       <c r="J124" s="68"/>
     </row>
-    <row r="125" spans="1:10" s="73" customFormat="1">
+    <row r="125" spans="1:10" s="73" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A125" s="27" t="s">
         <v>69</v>
       </c>
@@ -5180,7 +5180,7 @@
       </c>
       <c r="J125" s="68"/>
     </row>
-    <row r="126" spans="1:10" s="73" customFormat="1" ht="14.25">
+    <row r="126" spans="1:10" s="73" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A126" s="57" t="s">
         <v>101</v>
       </c>
@@ -5208,7 +5208,7 @@
       </c>
       <c r="J126" s="68"/>
     </row>
-    <row r="127" spans="1:10">
+    <row r="127" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A127" s="59" t="s">
         <v>71</v>
       </c>
@@ -5236,7 +5236,7 @@
       </c>
       <c r="J127" s="68"/>
     </row>
-    <row r="128" spans="1:10">
+    <row r="128" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A128" s="57" t="s">
         <v>72</v>
       </c>
@@ -5263,7 +5263,7 @@
       </c>
       <c r="J128" s="68"/>
     </row>
-    <row r="129" spans="1:10">
+    <row r="129" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A129" s="27" t="s">
         <v>73</v>
       </c>
@@ -5291,7 +5291,7 @@
       </c>
       <c r="J129" s="68"/>
     </row>
-    <row r="130" spans="1:10">
+    <row r="130" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A130" s="20" t="s">
         <v>74</v>
       </c>
@@ -5318,7 +5318,7 @@
       </c>
       <c r="J130" s="68"/>
     </row>
-    <row r="131" spans="1:10">
+    <row r="131" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A131" s="27" t="s">
         <v>75</v>
       </c>
@@ -5346,7 +5346,7 @@
       </c>
       <c r="J131" s="68"/>
     </row>
-    <row r="132" spans="1:10">
+    <row r="132" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A132" s="57" t="s">
         <v>76</v>
       </c>
@@ -5372,7 +5372,7 @@
         <v>1060.4055484272631</v>
       </c>
     </row>
-    <row r="133" spans="1:10">
+    <row r="133" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A133" s="59" t="s">
         <v>77</v>
       </c>
@@ -5400,7 +5400,7 @@
       </c>
       <c r="J133" s="19"/>
     </row>
-    <row r="134" spans="1:10">
+    <row r="134" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A134" s="57" t="s">
         <v>78</v>
       </c>
@@ -5427,7 +5427,7 @@
       </c>
       <c r="J134" s="68"/>
     </row>
-    <row r="135" spans="1:10">
+    <row r="135" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A135" s="27" t="s">
         <v>79</v>
       </c>
@@ -5455,7 +5455,7 @@
       </c>
       <c r="J135" s="68"/>
     </row>
-    <row r="136" spans="1:10">
+    <row r="136" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A136" s="20" t="s">
         <v>80</v>
       </c>
@@ -5482,7 +5482,7 @@
       </c>
       <c r="J136" s="68"/>
     </row>
-    <row r="137" spans="1:10" ht="15.75" thickBot="1">
+    <row r="137" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A137" s="93" t="s">
         <v>81</v>
       </c>
@@ -5510,7 +5510,7 @@
       </c>
       <c r="J137" s="68"/>
     </row>
-    <row r="138" spans="1:10" ht="16.5" thickTop="1" thickBot="1">
+    <row r="138" spans="1:10" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A138" s="21"/>
       <c r="B138" s="21"/>
       <c r="C138" s="66"/>
@@ -5521,7 +5521,7 @@
       <c r="H138" s="66"/>
       <c r="J138" s="68"/>
     </row>
-    <row r="139" spans="1:10" ht="18.75" thickBot="1">
+    <row r="139" spans="1:10" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A139" s="15" t="s">
         <v>102</v>
       </c>
@@ -5549,7 +5549,7 @@
       </c>
       <c r="J139" s="68"/>
     </row>
-    <row r="140" spans="1:10">
+    <row r="140" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A140" s="20" t="s">
         <v>103</v>
       </c>
@@ -5577,7 +5577,7 @@
       </c>
       <c r="J140" s="68"/>
     </row>
-    <row r="141" spans="1:10">
+    <row r="141" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A141" s="59" t="s">
         <v>104</v>
       </c>
@@ -5591,7 +5591,7 @@
       <c r="I141" s="70"/>
       <c r="J141" s="68"/>
     </row>
-    <row r="142" spans="1:10">
+    <row r="142" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A142" s="57" t="s">
         <v>105</v>
       </c>
@@ -5612,7 +5612,7 @@
       <c r="I142" s="67"/>
       <c r="J142" s="68"/>
     </row>
-    <row r="143" spans="1:10">
+    <row r="143" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A143" s="59" t="s">
         <v>106</v>
       </c>
@@ -5632,7 +5632,7 @@
       <c r="I143" s="70"/>
       <c r="J143" s="68"/>
     </row>
-    <row r="144" spans="1:10">
+    <row r="144" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A144" s="57" t="s">
         <v>107</v>
       </c>
@@ -5659,7 +5659,7 @@
       </c>
       <c r="J144" s="68"/>
     </row>
-    <row r="145" spans="1:10">
+    <row r="145" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A145" s="59" t="s">
         <v>108</v>
       </c>
@@ -5681,7 +5681,7 @@
       <c r="I145" s="70"/>
       <c r="J145" s="68"/>
     </row>
-    <row r="146" spans="1:10">
+    <row r="146" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A146" s="57" t="s">
         <v>109</v>
       </c>
@@ -5708,7 +5708,7 @@
       </c>
       <c r="J146" s="68"/>
     </row>
-    <row r="147" spans="1:10">
+    <row r="147" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A147" s="59" t="s">
         <v>110</v>
       </c>
@@ -5736,7 +5736,7 @@
       </c>
       <c r="J147" s="68"/>
     </row>
-    <row r="148" spans="1:10">
+    <row r="148" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A148" s="57" t="s">
         <v>105</v>
       </c>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="J148" s="68"/>
     </row>
-    <row r="149" spans="1:10">
+    <row r="149" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A149" s="59" t="s">
         <v>107</v>
       </c>
@@ -5791,7 +5791,7 @@
       </c>
       <c r="J149" s="34"/>
     </row>
-    <row r="150" spans="1:10">
+    <row r="150" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A150" s="57" t="s">
         <v>109</v>
       </c>
@@ -5817,7 +5817,7 @@
         <v>39.010000009234588</v>
       </c>
     </row>
-    <row r="151" spans="1:10">
+    <row r="151" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A151" s="27" t="s">
         <v>111</v>
       </c>
@@ -5844,7 +5844,7 @@
         <v>5.2116030849019062</v>
       </c>
     </row>
-    <row r="152" spans="1:10">
+    <row r="152" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A152" s="57" t="s">
         <v>112</v>
       </c>
@@ -5864,7 +5864,7 @@
       <c r="H152" s="66"/>
       <c r="I152" s="67"/>
     </row>
-    <row r="153" spans="1:10">
+    <row r="153" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A153" s="59" t="s">
         <v>113</v>
       </c>
@@ -5891,7 +5891,7 @@
         <v>2.5205571355626204</v>
       </c>
     </row>
-    <row r="154" spans="1:10">
+    <row r="154" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A154" s="57" t="s">
         <v>114</v>
       </c>
@@ -5917,7 +5917,7 @@
         <v>2.6910459493392862</v>
       </c>
     </row>
-    <row r="155" spans="1:10">
+    <row r="155" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A155" s="59"/>
       <c r="B155" s="60"/>
       <c r="C155" s="69"/>
@@ -5928,7 +5928,7 @@
       <c r="H155" s="69"/>
       <c r="I155" s="70"/>
     </row>
-    <row r="156" spans="1:10" ht="15.75" thickBot="1">
+    <row r="156" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A156" s="38" t="s">
         <v>115</v>
       </c>
@@ -5955,7 +5955,7 @@
         <v>7.8382324901165461</v>
       </c>
     </row>
-    <row r="157" spans="1:10">
+    <row r="157" spans="1:10" x14ac:dyDescent="0.35">
       <c r="C157" s="32"/>
       <c r="D157" s="32"/>
       <c r="E157" s="32"/>
@@ -5964,7 +5964,7 @@
       <c r="H157" s="32"/>
       <c r="I157" s="32"/>
     </row>
-    <row r="158" spans="1:10">
+    <row r="158" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A158" s="58" t="s">
         <v>116</v>
       </c>
@@ -5987,12 +5987,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4E39369-50AE-4D5B-A91E-C3BF3A8489A4}">
   <dimension ref="A1:AE9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="18.75" thickBot="1">
+    <row r="1" spans="1:31" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B1" s="17">
         <v>2028</v>
       </c>
@@ -6015,7 +6015,7 @@
         <v>2055</v>
       </c>
     </row>
-    <row r="2" spans="1:31">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>117</v>
       </c>
@@ -6048,7 +6048,7 @@
         <v>0.42851499116440761</v>
       </c>
     </row>
-    <row r="3" spans="1:31">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>118</v>
       </c>
@@ -6081,12 +6081,12 @@
         <v>0.72106646255644558</v>
       </c>
     </row>
-    <row r="5" spans="1:31">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="6" spans="1:31">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>117</v>
       </c>
@@ -6119,7 +6119,7 @@
         <v>0.59511818843685693</v>
       </c>
     </row>
-    <row r="8" spans="1:31">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>119</v>
       </c>
@@ -6214,7 +6214,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="9" spans="1:31">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>117</v>
       </c>
@@ -6347,14 +6347,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0277EEC5-A757-48AB-8FE9-C61BFB5A988F}">
   <dimension ref="A1:AE27"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:31">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="3" spans="1:31">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>121</v>
       </c>
@@ -6449,7 +6449,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="4" spans="1:31">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -6544,7 +6544,7 @@
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="5" spans="1:31">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -6639,7 +6639,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="6" spans="1:31">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>122</v>
       </c>
@@ -6734,7 +6734,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="7" spans="1:31">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>0</v>
       </c>
@@ -6829,7 +6829,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:31">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>1</v>
       </c>
@@ -6924,7 +6924,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:31">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -7019,7 +7019,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:31">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>2</v>
       </c>
@@ -7114,7 +7114,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:31">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -7209,7 +7209,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:31">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -7304,7 +7304,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:31">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>123</v>
       </c>
@@ -7399,7 +7399,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:31">
+    <row r="14" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>6</v>
       </c>
@@ -7494,7 +7494,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="15" spans="1:31">
+    <row r="15" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>31</v>
       </c>
@@ -7589,7 +7589,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="16" spans="1:31">
+    <row r="16" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>9</v>
       </c>
@@ -7684,7 +7684,7 @@
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="17" spans="1:31">
+    <row r="17" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>12</v>
       </c>
@@ -7779,7 +7779,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:31">
+    <row r="18" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>13</v>
       </c>
@@ -7874,7 +7874,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="19" spans="1:31">
+    <row r="19" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>14</v>
       </c>
@@ -7969,7 +7969,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="20" spans="1:31">
+    <row r="20" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>15</v>
       </c>
@@ -8064,7 +8064,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="21" spans="1:31">
+    <row r="21" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>26</v>
       </c>
@@ -8159,7 +8159,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="22" spans="1:31">
+    <row r="22" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>27</v>
       </c>
@@ -8254,7 +8254,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="23" spans="1:31">
+    <row r="23" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>28</v>
       </c>
@@ -8349,7 +8349,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="24" spans="1:31">
+    <row r="24" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>29</v>
       </c>
@@ -8444,7 +8444,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="25" spans="1:31">
+    <row r="25" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>30</v>
       </c>
@@ -8539,7 +8539,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="26" spans="1:31">
+    <row r="26" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>32</v>
       </c>
@@ -8634,7 +8634,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="27" spans="1:31">
+    <row r="27" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>33</v>
       </c>
@@ -8739,109 +8739,112 @@
   <sheetPr>
     <tabColor rgb="FF002060"/>
   </sheetPr>
-  <dimension ref="A1:AE25"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:AF25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="26.42578125" customWidth="1"/>
-    <col min="2" max="3" width="11" customWidth="1"/>
+    <col min="1" max="1" width="26.453125" customWidth="1"/>
+    <col min="2" max="4" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="30">
+    <row r="1" spans="1:32" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
         <v>16</v>
       </c>
       <c r="B1" s="5">
+        <v>2020</v>
+      </c>
+      <c r="C1" s="5">
         <v>2021</v>
       </c>
-      <c r="C1" s="5">
+      <c r="D1" s="5">
         <v>2022</v>
       </c>
-      <c r="D1" s="5">
+      <c r="E1" s="5">
         <v>2023</v>
       </c>
-      <c r="E1" s="5">
+      <c r="F1" s="5">
         <v>2024</v>
       </c>
-      <c r="F1" s="5">
+      <c r="G1" s="5">
         <v>2025</v>
       </c>
-      <c r="G1" s="5">
+      <c r="H1" s="5">
         <v>2026</v>
       </c>
-      <c r="H1" s="5">
+      <c r="I1" s="5">
         <v>2027</v>
       </c>
-      <c r="I1" s="5">
+      <c r="J1" s="5">
         <v>2028</v>
       </c>
-      <c r="J1" s="5">
+      <c r="K1" s="5">
         <v>2029</v>
       </c>
-      <c r="K1" s="5">
+      <c r="L1" s="5">
         <v>2030</v>
       </c>
-      <c r="L1" s="5">
+      <c r="M1" s="5">
         <v>2031</v>
       </c>
-      <c r="M1" s="5">
+      <c r="N1" s="5">
         <v>2032</v>
       </c>
-      <c r="N1" s="5">
+      <c r="O1" s="5">
         <v>2033</v>
       </c>
-      <c r="O1" s="5">
+      <c r="P1" s="5">
         <v>2034</v>
       </c>
-      <c r="P1" s="5">
+      <c r="Q1" s="5">
         <v>2035</v>
       </c>
-      <c r="Q1" s="5">
+      <c r="R1" s="5">
         <v>2036</v>
       </c>
-      <c r="R1" s="5">
+      <c r="S1" s="5">
         <v>2037</v>
       </c>
-      <c r="S1" s="5">
+      <c r="T1" s="5">
         <v>2038</v>
       </c>
-      <c r="T1" s="5">
+      <c r="U1" s="5">
         <v>2039</v>
       </c>
-      <c r="U1" s="5">
+      <c r="V1" s="5">
         <v>2040</v>
       </c>
-      <c r="V1" s="5">
+      <c r="W1" s="5">
         <v>2041</v>
       </c>
-      <c r="W1" s="5">
+      <c r="X1" s="5">
         <v>2042</v>
       </c>
-      <c r="X1" s="5">
+      <c r="Y1" s="5">
         <v>2043</v>
       </c>
-      <c r="Y1" s="5">
+      <c r="Z1" s="5">
         <v>2044</v>
       </c>
-      <c r="Z1" s="5">
+      <c r="AA1" s="5">
         <v>2045</v>
       </c>
-      <c r="AA1" s="5">
+      <c r="AB1" s="5">
         <v>2046</v>
       </c>
-      <c r="AB1" s="5">
+      <c r="AC1" s="5">
         <v>2047</v>
       </c>
-      <c r="AC1" s="5">
+      <c r="AD1" s="5">
         <v>2048</v>
       </c>
-      <c r="AD1" s="5">
+      <c r="AE1" s="5">
         <v>2049</v>
       </c>
-      <c r="AE1" s="5">
+      <c r="AF1" s="5">
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -8935,8 +8938,11 @@
       <c r="AE2" s="3">
         <v>0.85</v>
       </c>
-    </row>
-    <row r="3" spans="1:31">
+      <c r="AF2" s="3">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="3" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -9030,8 +9036,11 @@
       <c r="AE3" s="3">
         <v>0.95</v>
       </c>
-    </row>
-    <row r="4" spans="1:31">
+      <c r="AF3" s="3">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="4" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -9125,8 +9134,11 @@
       <c r="AE4" s="3">
         <v>0.95</v>
       </c>
-    </row>
-    <row r="5" spans="1:31">
+      <c r="AF4" s="3">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="5" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>0</v>
       </c>
@@ -9220,8 +9232,11 @@
       <c r="AE5" s="3">
         <v>0.91</v>
       </c>
-    </row>
-    <row r="6" spans="1:31">
+      <c r="AF5" s="3">
+        <v>0.91</v>
+      </c>
+    </row>
+    <row r="6" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>1</v>
       </c>
@@ -9315,8 +9330,11 @@
       <c r="AE6" s="3">
         <v>0.95</v>
       </c>
-    </row>
-    <row r="7" spans="1:31">
+      <c r="AF6" s="3">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="7" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -9410,8 +9428,11 @@
       <c r="AE7" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:31">
+      <c r="AF7" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>2</v>
       </c>
@@ -9505,8 +9526,11 @@
       <c r="AE8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:31">
+      <c r="AF8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -9600,8 +9624,11 @@
       <c r="AE9" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:31">
+      <c r="AF9" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -9695,8 +9722,11 @@
       <c r="AE10" s="3">
         <v>0.95</v>
       </c>
-    </row>
-    <row r="11" spans="1:31">
+      <c r="AF10" s="3">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>5</v>
       </c>
@@ -9790,8 +9820,11 @@
       <c r="AE11" s="3">
         <v>0.95</v>
       </c>
-    </row>
-    <row r="12" spans="1:31">
+      <c r="AF11" s="3">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>6</v>
       </c>
@@ -9885,8 +9918,11 @@
       <c r="AE12" s="3">
         <v>0.95</v>
       </c>
-    </row>
-    <row r="13" spans="1:31">
+      <c r="AF12" s="3">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>31</v>
       </c>
@@ -9980,8 +10016,11 @@
       <c r="AE13" s="3">
         <v>0.95</v>
       </c>
-    </row>
-    <row r="14" spans="1:31">
+      <c r="AF13" s="3">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>9</v>
       </c>
@@ -10075,8 +10114,11 @@
       <c r="AE14" s="3">
         <v>0.95</v>
       </c>
-    </row>
-    <row r="15" spans="1:31">
+      <c r="AF14" s="3">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>12</v>
       </c>
@@ -10170,8 +10212,11 @@
       <c r="AE15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:31">
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>13</v>
       </c>
@@ -10265,8 +10310,11 @@
       <c r="AE16" s="3">
         <v>0.95</v>
       </c>
-    </row>
-    <row r="17" spans="1:31">
+      <c r="AF16" s="3">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="17" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>14</v>
       </c>
@@ -10360,8 +10408,11 @@
       <c r="AE17" s="3">
         <v>0.95</v>
       </c>
-    </row>
-    <row r="18" spans="1:31">
+      <c r="AF17" s="3">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="18" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>15</v>
       </c>
@@ -10455,8 +10506,11 @@
       <c r="AE18" s="3">
         <v>0.95</v>
       </c>
-    </row>
-    <row r="19" spans="1:31">
+      <c r="AF18" s="3">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="19" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>26</v>
       </c>
@@ -10465,11 +10519,11 @@
         <v>0.85</v>
       </c>
       <c r="C19" s="3">
-        <f t="shared" ref="C19:AE19" si="0">C2</f>
+        <f>C2</f>
         <v>0.85</v>
       </c>
       <c r="D19" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="D19:AF19" si="0">D2</f>
         <v>0.85</v>
       </c>
       <c r="E19" s="3">
@@ -10580,8 +10634,12 @@
         <f t="shared" si="0"/>
         <v>0.85</v>
       </c>
-    </row>
-    <row r="20" spans="1:31">
+      <c r="AF19" s="3">
+        <f t="shared" si="0"/>
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="20" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>27</v>
       </c>
@@ -10590,11 +10648,11 @@
         <v>0.95</v>
       </c>
       <c r="C20" s="3">
-        <f t="shared" ref="C20:AE20" si="1">C4</f>
+        <f>C4</f>
         <v>0.95</v>
       </c>
       <c r="D20" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="D20:AF20" si="1">D4</f>
         <v>0.95</v>
       </c>
       <c r="E20" s="3">
@@ -10705,8 +10763,12 @@
         <f t="shared" si="1"/>
         <v>0.95</v>
       </c>
-    </row>
-    <row r="21" spans="1:31">
+      <c r="AF20" s="3">
+        <f t="shared" si="1"/>
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="21" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>28</v>
       </c>
@@ -10715,11 +10777,11 @@
         <v>0.95</v>
       </c>
       <c r="C21" s="3">
-        <f t="shared" ref="C21:AE21" si="2">C10</f>
+        <f>C10</f>
         <v>0.95</v>
       </c>
       <c r="D21" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="D21:AF21" si="2">D10</f>
         <v>0.95</v>
       </c>
       <c r="E21" s="3">
@@ -10830,8 +10892,12 @@
         <f t="shared" si="2"/>
         <v>0.95</v>
       </c>
-    </row>
-    <row r="22" spans="1:31">
+      <c r="AF21" s="3">
+        <f t="shared" si="2"/>
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="22" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>29</v>
       </c>
@@ -10840,11 +10906,11 @@
         <v>0.95</v>
       </c>
       <c r="C22" s="3">
-        <f t="shared" ref="C22:AE22" si="3">C14</f>
+        <f>C14</f>
         <v>0.95</v>
       </c>
       <c r="D22" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="D22:AF22" si="3">D14</f>
         <v>0.95</v>
       </c>
       <c r="E22" s="3">
@@ -10955,8 +11021,12 @@
         <f t="shared" si="3"/>
         <v>0.95</v>
       </c>
-    </row>
-    <row r="23" spans="1:31">
+      <c r="AF22" s="3">
+        <f t="shared" si="3"/>
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="23" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>30</v>
       </c>
@@ -10965,11 +11035,11 @@
         <v>0.91</v>
       </c>
       <c r="C23" s="3">
-        <f t="shared" ref="C23:AE23" si="4">C5</f>
+        <f>C5</f>
         <v>0.91</v>
       </c>
       <c r="D23" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="D23:AF23" si="4">D5</f>
         <v>0.91</v>
       </c>
       <c r="E23" s="3">
@@ -11080,8 +11150,12 @@
         <f t="shared" si="4"/>
         <v>0.91</v>
       </c>
-    </row>
-    <row r="24" spans="1:31">
+      <c r="AF23" s="3">
+        <f t="shared" si="4"/>
+        <v>0.91</v>
+      </c>
+    </row>
+    <row r="24" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A24" s="7" t="s">
         <v>32</v>
       </c>
@@ -11090,11 +11164,11 @@
         <v>0.95</v>
       </c>
       <c r="C24" s="3">
-        <f t="shared" ref="C24:AE24" si="5">C4</f>
+        <f>C4</f>
         <v>0.95</v>
       </c>
       <c r="D24" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="D24:AF24" si="5">D4</f>
         <v>0.95</v>
       </c>
       <c r="E24" s="3">
@@ -11205,8 +11279,12 @@
         <f t="shared" si="5"/>
         <v>0.95</v>
       </c>
-    </row>
-    <row r="25" spans="1:31">
+      <c r="AF24" s="3">
+        <f t="shared" si="5"/>
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="25" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A25" s="7" t="s">
         <v>33</v>
       </c>
@@ -11215,11 +11293,11 @@
         <v>0.95</v>
       </c>
       <c r="C25" s="3">
-        <f t="shared" ref="C25:AE25" si="6">C4</f>
+        <f>C4</f>
         <v>0.95</v>
       </c>
       <c r="D25" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="D25:AF25" si="6">D4</f>
         <v>0.95</v>
       </c>
       <c r="E25" s="3">
@@ -11327,6 +11405,10 @@
         <v>0.95</v>
       </c>
       <c r="AE25" s="3">
+        <f t="shared" si="6"/>
+        <v>0.95</v>
+      </c>
+      <c r="AF25" s="3">
         <f t="shared" si="6"/>
         <v>0.95</v>
       </c>
@@ -11337,6 +11419,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002041A8AB53924247A2770D65450F5227" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="90fff4f083191fe75a03dbd50c7739fc">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1659011e-6b88-4225-9a61-aaf33aaf19e8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7fee88694a371868130ae0617c69143c" ns2:_="">
     <xsd:import namespace="1659011e-6b88-4225-9a61-aaf33aaf19e8"/>
@@ -11480,29 +11577,37 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A9328D06-F063-46AB-B326-B3039701A42C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F51BFEEE-333B-46AA-A98D-36596FD2A45F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B68633F6-8174-4B75-B374-2384FC5DB6BB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B68633F6-8174-4B75-B374-2384FC5DB6BB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F51BFEEE-333B-46AA-A98D-36596FD2A45F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A9328D06-F063-46AB-B326-B3039701A42C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="1659011e-6b88-4225-9a61-aaf33aaf19e8"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>